--- a/MAJSushiConfig/ig/observations-summary.xlsx
+++ b/MAJSushiConfig/ig/observations-summary.xlsx
@@ -77,7 +77,7 @@
     <t>Observation Category Codes#survey</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-evaluation-type|0.1.0 (extensible)</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-evaluation-type|0.1.0 (extensible)</t>
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
